--- a/outputs/Block2_National_Outcome_OOF_v12.xlsx
+++ b/outputs/Block2_National_Outcome_OOF_v12.xlsx
@@ -954,13 +954,13 @@
         <v>8.000000000000002</v>
       </c>
       <c r="E23">
-        <v>0.3420000000001311</v>
+        <v>0.3420000000001255</v>
       </c>
       <c r="F23">
-        <v>-7.657999999999871</v>
+        <v>-7.657999999999876</v>
       </c>
       <c r="G23">
-        <v>7.657999999999871</v>
+        <v>7.657999999999876</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1437,13 +1437,13 @@
         <v>-6.800000000000001</v>
       </c>
       <c r="E44">
-        <v>-1.600400000000041</v>
+        <v>-1.600400000000046</v>
       </c>
       <c r="F44">
-        <v>5.19959999999996</v>
+        <v>5.199599999999954</v>
       </c>
       <c r="G44">
-        <v>5.19959999999996</v>
+        <v>5.199599999999954</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2242,13 +2242,13 @@
         <v>-6.800000000000001</v>
       </c>
       <c r="E79">
-        <v>-1.255768581635441</v>
+        <v>-1.255768581635436</v>
       </c>
       <c r="F79">
-        <v>5.544231418364559</v>
+        <v>5.544231418364565</v>
       </c>
       <c r="G79">
-        <v>5.544231418364559</v>
+        <v>5.544231418364565</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2886,13 +2886,13 @@
         <v>-5.699999999999999</v>
       </c>
       <c r="E107">
-        <v>-0.4551999999999556</v>
+        <v>-0.4551999999999501</v>
       </c>
       <c r="F107">
-        <v>5.244800000000044</v>
+        <v>5.244800000000049</v>
       </c>
       <c r="G107">
-        <v>5.244800000000044</v>
+        <v>5.244800000000049</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3852,13 +3852,13 @@
         <v>8.600000000000001</v>
       </c>
       <c r="E149">
-        <v>-0.5244000000000582</v>
+        <v>-0.5244000000000526</v>
       </c>
       <c r="F149">
-        <v>-9.12440000000006</v>
+        <v>-9.124400000000055</v>
       </c>
       <c r="G149">
-        <v>9.12440000000006</v>
+        <v>9.124400000000055</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4174,13 +4174,13 @@
         <v>8.600000000000001</v>
       </c>
       <c r="E163">
-        <v>-0.05467977032406757</v>
+        <v>-0.05467977032406202</v>
       </c>
       <c r="F163">
-        <v>-8.654679770324069</v>
+        <v>-8.654679770324064</v>
       </c>
       <c r="G163">
-        <v>8.654679770324069</v>
+        <v>8.654679770324064</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5140,13 +5140,13 @@
         <v>-2.700000000000002</v>
       </c>
       <c r="E205">
-        <v>-1.048624949950233</v>
+        <v>-1.048624949950228</v>
       </c>
       <c r="F205">
-        <v>1.651375050049769</v>
+        <v>1.651375050049775</v>
       </c>
       <c r="G205">
-        <v>1.651375050049769</v>
+        <v>1.651375050049775</v>
       </c>
     </row>
     <row r="206" spans="1:7">

--- a/outputs/Block2_National_Outcome_OOF_v12.xlsx
+++ b/outputs/Block2_National_Outcome_OOF_v12.xlsx
@@ -1920,13 +1920,13 @@
         <v>-6.800000000000001</v>
       </c>
       <c r="E65">
-        <v>-0.8272000000000279</v>
+        <v>-0.8272000000000224</v>
       </c>
       <c r="F65">
-        <v>5.972799999999973</v>
+        <v>5.972799999999978</v>
       </c>
       <c r="G65">
-        <v>5.972799999999973</v>
+        <v>5.972799999999978</v>
       </c>
     </row>
     <row r="66" spans="1:7">

--- a/outputs/Block2_National_Outcome_OOF_v12.xlsx
+++ b/outputs/Block2_National_Outcome_OOF_v12.xlsx
@@ -568,13 +568,13 @@
         <v>8.000000000000002</v>
       </c>
       <c r="E7">
-        <v>2.543512328404107</v>
+        <v>2.543512328404118</v>
       </c>
       <c r="F7">
-        <v>-5.456487671595895</v>
+        <v>-5.456487671595884</v>
       </c>
       <c r="G7">
-        <v>5.456487671595895</v>
+        <v>5.456487671595884</v>
       </c>
     </row>
     <row r="8" spans="1:7">

--- a/outputs/Block2_National_Outcome_OOF_v12.xlsx
+++ b/outputs/Block2_National_Outcome_OOF_v12.xlsx
@@ -568,13 +568,13 @@
         <v>8.000000000000002</v>
       </c>
       <c r="E7">
-        <v>2.543512328404118</v>
+        <v>2.543512328404107</v>
       </c>
       <c r="F7">
-        <v>-5.456487671595884</v>
+        <v>-5.456487671595895</v>
       </c>
       <c r="G7">
-        <v>5.456487671595884</v>
+        <v>5.456487671595895</v>
       </c>
     </row>
     <row r="8" spans="1:7">

--- a/outputs/Block2_National_Outcome_OOF_v12.xlsx
+++ b/outputs/Block2_National_Outcome_OOF_v12.xlsx
@@ -798,13 +798,13 @@
         <v>-5.699999999999999</v>
       </c>
       <c r="E17">
-        <v>-0.2119999999999178</v>
+        <v>-0.2119999999999234</v>
       </c>
       <c r="F17">
-        <v>5.488000000000081</v>
+        <v>5.488000000000076</v>
       </c>
       <c r="G17">
-        <v>5.488000000000081</v>
+        <v>5.488000000000076</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -844,13 +844,13 @@
         <v>-5.699999999999999</v>
       </c>
       <c r="E19">
-        <v>0.04723833384575049</v>
+        <v>0.04723833384574494</v>
       </c>
       <c r="F19">
-        <v>5.74723833384575</v>
+        <v>5.747238333845744</v>
       </c>
       <c r="G19">
-        <v>5.74723833384575</v>
+        <v>5.747238333845744</v>
       </c>
     </row>
     <row r="20" spans="1:7">

--- a/outputs/Block2_National_Outcome_OOF_v12.xlsx
+++ b/outputs/Block2_National_Outcome_OOF_v12.xlsx
@@ -798,13 +798,13 @@
         <v>-5.699999999999999</v>
       </c>
       <c r="E17">
-        <v>-0.2119999999999234</v>
+        <v>-0.2119999999999178</v>
       </c>
       <c r="F17">
-        <v>5.488000000000076</v>
+        <v>5.488000000000081</v>
       </c>
       <c r="G17">
-        <v>5.488000000000076</v>
+        <v>5.488000000000081</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -844,13 +844,13 @@
         <v>-5.699999999999999</v>
       </c>
       <c r="E19">
-        <v>0.04723833384574494</v>
+        <v>0.04723833384575049</v>
       </c>
       <c r="F19">
-        <v>5.747238333845744</v>
+        <v>5.74723833384575</v>
       </c>
       <c r="G19">
-        <v>5.747238333845744</v>
+        <v>5.74723833384575</v>
       </c>
     </row>
     <row r="20" spans="1:7">

--- a/outputs/Block2_National_Outcome_OOF_v12.xlsx
+++ b/outputs/Block2_National_Outcome_OOF_v12.xlsx
@@ -568,13 +568,13 @@
         <v>8.000000000000002</v>
       </c>
       <c r="E7">
-        <v>2.543512328404107</v>
+        <v>2.543512328404118</v>
       </c>
       <c r="F7">
-        <v>-5.456487671595895</v>
+        <v>-5.456487671595884</v>
       </c>
       <c r="G7">
-        <v>5.456487671595895</v>
+        <v>5.456487671595884</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -936,13 +936,13 @@
         <v>8.600000000000001</v>
       </c>
       <c r="E23">
-        <v>-0.3532000000000424</v>
+        <v>-0.3532000000000368</v>
       </c>
       <c r="F23">
-        <v>-8.953200000000043</v>
+        <v>-8.953200000000038</v>
       </c>
       <c r="G23">
-        <v>8.953200000000043</v>
+        <v>8.953200000000038</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1005,13 +1005,13 @@
         <v>-2.700000000000002</v>
       </c>
       <c r="E26">
-        <v>-3.828400000000032</v>
+        <v>-3.828400000000026</v>
       </c>
       <c r="F26">
-        <v>-1.128400000000029</v>
+        <v>-1.128400000000024</v>
       </c>
       <c r="G26">
-        <v>1.128400000000029</v>
+        <v>1.128400000000024</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1120,13 +1120,13 @@
         <v>-2.700000000000002</v>
       </c>
       <c r="E31">
-        <v>-3.065054916225662</v>
+        <v>-3.065054916225657</v>
       </c>
       <c r="F31">
-        <v>-0.36505491622566</v>
+        <v>-0.3650549162256547</v>
       </c>
       <c r="G31">
-        <v>0.36505491622566</v>
+        <v>0.3650549162256547</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_National_Outcome_OOF_v12.xlsx
+++ b/outputs/Block2_National_Outcome_OOF_v12.xlsx
@@ -522,13 +522,13 @@
         <v>8.000000000000002</v>
       </c>
       <c r="E5">
-        <v>0.6596000000001545</v>
+        <v>0.659600000000149</v>
       </c>
       <c r="F5">
-        <v>-7.340399999999847</v>
+        <v>-7.340399999999853</v>
       </c>
       <c r="G5">
-        <v>7.340399999999847</v>
+        <v>7.340399999999853</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -798,13 +798,13 @@
         <v>-5.699999999999999</v>
       </c>
       <c r="E17">
-        <v>-0.2119999999999234</v>
+        <v>-0.2119999999999289</v>
       </c>
       <c r="F17">
-        <v>5.488000000000076</v>
+        <v>5.488000000000071</v>
       </c>
       <c r="G17">
-        <v>5.488000000000076</v>
+        <v>5.488000000000071</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -936,13 +936,13 @@
         <v>8.600000000000001</v>
       </c>
       <c r="E23">
-        <v>-0.3532000000000368</v>
+        <v>-0.3532000000000424</v>
       </c>
       <c r="F23">
-        <v>-8.953200000000038</v>
+        <v>-8.953200000000043</v>
       </c>
       <c r="G23">
-        <v>8.953200000000038</v>
+        <v>8.953200000000043</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1120,13 +1120,13 @@
         <v>-2.700000000000002</v>
       </c>
       <c r="E31">
-        <v>-3.065054916225657</v>
+        <v>-3.065054916225662</v>
       </c>
       <c r="F31">
-        <v>-0.3650549162256547</v>
+        <v>-0.36505491622566</v>
       </c>
       <c r="G31">
-        <v>0.3650549162256547</v>
+        <v>0.36505491622566</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_National_Outcome_OOF_v12.xlsx
+++ b/outputs/Block2_National_Outcome_OOF_v12.xlsx
@@ -522,13 +522,13 @@
         <v>8.000000000000002</v>
       </c>
       <c r="E5">
-        <v>0.659600000000149</v>
+        <v>0.6596000000001545</v>
       </c>
       <c r="F5">
-        <v>-7.340399999999853</v>
+        <v>-7.340399999999847</v>
       </c>
       <c r="G5">
-        <v>7.340399999999853</v>
+        <v>7.340399999999847</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -568,13 +568,13 @@
         <v>8.000000000000002</v>
       </c>
       <c r="E7">
-        <v>2.543512328404118</v>
+        <v>2.543512328404107</v>
       </c>
       <c r="F7">
-        <v>-5.456487671595884</v>
+        <v>-5.456487671595895</v>
       </c>
       <c r="G7">
-        <v>5.456487671595884</v>
+        <v>5.456487671595895</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -798,13 +798,13 @@
         <v>-5.699999999999999</v>
       </c>
       <c r="E17">
-        <v>-0.2119999999999289</v>
+        <v>-0.2119999999999178</v>
       </c>
       <c r="F17">
-        <v>5.488000000000071</v>
+        <v>5.488000000000081</v>
       </c>
       <c r="G17">
-        <v>5.488000000000071</v>
+        <v>5.488000000000081</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -844,13 +844,13 @@
         <v>-5.699999999999999</v>
       </c>
       <c r="E19">
-        <v>0.04723833384574494</v>
+        <v>0.04723833384575049</v>
       </c>
       <c r="F19">
-        <v>5.747238333845744</v>
+        <v>5.74723833384575</v>
       </c>
       <c r="G19">
-        <v>5.747238333845744</v>
+        <v>5.74723833384575</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1005,13 +1005,13 @@
         <v>-2.700000000000002</v>
       </c>
       <c r="E26">
-        <v>-3.828400000000026</v>
+        <v>-3.828400000000032</v>
       </c>
       <c r="F26">
-        <v>-1.128400000000024</v>
+        <v>-1.128400000000029</v>
       </c>
       <c r="G26">
-        <v>1.128400000000024</v>
+        <v>1.128400000000029</v>
       </c>
     </row>
     <row r="27" spans="1:7">

--- a/outputs/Block2_National_Outcome_OOF_v12.xlsx
+++ b/outputs/Block2_National_Outcome_OOF_v12.xlsx
@@ -1120,13 +1120,13 @@
         <v>-2.700000000000002</v>
       </c>
       <c r="E31">
-        <v>-3.065054916225662</v>
+        <v>-3.065054916225651</v>
       </c>
       <c r="F31">
-        <v>-0.36505491622566</v>
+        <v>-0.3650549162256489</v>
       </c>
       <c r="G31">
-        <v>0.36505491622566</v>
+        <v>0.3650549162256489</v>
       </c>
     </row>
   </sheetData>
